--- a/AAII_Financials/Quarterly/ULCC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ULCC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>ULCC</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1279000</v>
+      </c>
+      <c r="E8" s="3">
         <v>992000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>997000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>886000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>929000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>912000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1002000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>935000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>973000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>865000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>891000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>883000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>967000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>848000</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>906000</v>
       </c>
       <c r="R8" s="3">
         <v>906000</v>
       </c>
       <c r="S8" s="3">
+        <v>906000</v>
+      </c>
+      <c r="T8" s="3">
         <v>909000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>605000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>609000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>630000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>550000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>271000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>267000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>245000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>194000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>544000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>655000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>669000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>637000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1138000</v>
+        <v>1229000</v>
       </c>
       <c r="E9" s="3">
+        <v>1065000</v>
+      </c>
+      <c r="F9" s="3">
         <v>946000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>891000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>903000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>879000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>891000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>884000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>841000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>820000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>843000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>779000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>795000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>459000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>446000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>468000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>343000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>317000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>294000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>272000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>222000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>187000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>177000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>270000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>738000</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-146000</v>
+        <v>50000</v>
       </c>
       <c r="E10" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="F10" s="3">
         <v>51000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>102000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>89000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>71000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>188000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>53000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>447000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>460000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>441000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>262000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>292000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>336000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>278000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>49000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>80000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>385000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-69000</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,88 +1279,91 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-47000</v>
+        <v>-21000</v>
       </c>
       <c r="E14" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-145000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-67000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-34000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-56000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-76000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-110000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-77000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-71000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-49000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-40000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-17000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-12000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-72000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-87000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-136000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-97000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1351,64 +1371,67 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>62000</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F15" s="3">
         <v>26000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>19000</v>
       </c>
       <c r="J15" s="3">
         <v>19000</v>
       </c>
       <c r="K15" s="3">
+        <v>19000</v>
+      </c>
+      <c r="L15" s="3">
         <v>18000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>15000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>10000</v>
       </c>
       <c r="V15" s="3">
         <v>10000</v>
@@ -1417,31 +1440,34 @@
         <v>10000</v>
       </c>
       <c r="X15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>8000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>8000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>11000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>35000</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1322000</v>
+        <v>1397000</v>
       </c>
       <c r="E17" s="3">
+        <v>1212000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1093000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1030000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1038000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1014000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1033000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1026000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1025000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>967000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>943000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>977000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>905000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>912000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>861000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>850000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>902000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>758000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>695000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>587000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>532000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>363000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>451000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>326000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>587000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1612000</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-330000</v>
+        <v>-118000</v>
       </c>
       <c r="E18" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-96000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-144000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-109000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-102000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-91000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-52000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-102000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-52000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-94000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>62000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>45000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>56000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-153000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-86000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-92000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-184000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-81000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>68000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-943000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1725,142 +1759,148 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>1000</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1204000</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-268000</v>
+        <v>-88000</v>
       </c>
       <c r="E21" s="3">
+        <v>-195000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-70000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-120000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-88000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-82000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-72000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-86000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-38000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-81000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>74000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>59000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>67000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-140000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-75000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>54000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-173000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>86000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>296000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1868,266 +1908,275 @@
         <v>4000</v>
       </c>
       <c r="E22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F22" s="3">
         <v>3000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1000</v>
       </c>
       <c r="I22" s="3">
         <v>1000</v>
       </c>
       <c r="J22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>1000</v>
       </c>
       <c r="O22" s="3">
         <v>1000</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>1000</v>
       </c>
       <c r="T22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U22" s="3">
         <v>8000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1000</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8000</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-281000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-76000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-70000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-45000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>88000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>58000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-161000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-86000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>41000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>14000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-193000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>72000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>253000</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1000</v>
       </c>
       <c r="K24" s="3">
         <v>1000</v>
       </c>
       <c r="L24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>43000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-13000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>17000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-40000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-33000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>16000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58000</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-272000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>53000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-77000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-43000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>40000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-121000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-53000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-127000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>56000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>195000</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-272000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>53000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-77000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-70000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-43000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>53000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-32000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>71000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>40000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-121000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-53000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-127000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>56000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>195000</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2793,142 +2863,148 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-1000</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1204000</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-272000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>53000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-77000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-43000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-32000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>40000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-121000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-53000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-127000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>56000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>195000</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-272000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>53000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-77000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-43000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-32000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>40000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-121000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-53000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-127000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>56000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>195000</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>955000</v>
+      </c>
+      <c r="E41" s="3">
         <v>772000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>671000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>566000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>563000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>686000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>740000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>576000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>658000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>622000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>609000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>640000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>780000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>790000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>761000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>674000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>766000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>727000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>918000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>802000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>936000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>429000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>378000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E43" s="3">
         <v>185000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>169000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>165000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>158000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>161000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>149000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>194000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>188000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>173000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>159000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>157000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>112000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>118000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>153000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>127000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>120000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>104000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>82000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>239000</v>
-      </c>
-      <c r="W43" s="3">
-        <v>229000</v>
       </c>
       <c r="X43" s="3">
         <v>229000</v>
       </c>
       <c r="Y43" s="3">
+        <v>229000</v>
+      </c>
+      <c r="Z43" s="3">
         <v>207000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3532,53 +3625,56 @@
       <c r="AE43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E44" s="3">
         <v>106000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>90000</v>
       </c>
       <c r="F44" s="3">
         <v>90000</v>
       </c>
       <c r="G44" s="3">
+        <v>90000</v>
+      </c>
+      <c r="H44" s="3">
         <v>86000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>81000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>79000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>76000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>78000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>75000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>79000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>75000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>60000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>57000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -3621,80 +3717,83 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2000</v>
       </c>
       <c r="F45" s="3">
         <v>2000</v>
       </c>
       <c r="G45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>45000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>106000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>91000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>68000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>45000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>61000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>62000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>65000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3710,80 +3809,83 @@
       <c r="AE45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1306000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1098000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>958000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>847000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>832000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>953000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>990000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>910000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>947000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>903000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>871000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>936000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1009000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1042000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1020000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>892000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>954000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>876000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1037000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1092000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1226000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>720000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>650000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3799,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3843,8 +3948,8 @@
       <c r="P47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3888,80 +3993,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5084000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5316000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4813000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4728000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4638000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4306000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4090000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3939000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3447000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3273000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3112000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2898000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2865000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2710000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2618000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2591000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2594000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2612000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2678000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2569000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2469000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2426000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4010,7 +4121,7 @@
         <v>27000</v>
       </c>
       <c r="M49" s="3">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="N49" s="3">
         <v>28000</v>
@@ -4034,7 +4145,7 @@
         <v>28000</v>
       </c>
       <c r="U49" s="3">
-        <v>29000</v>
+        <v>28000</v>
       </c>
       <c r="V49" s="3">
         <v>29000</v>
@@ -4048,8 +4159,8 @@
       <c r="Y49" s="3">
         <v>29000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
+      <c r="Z49" s="3">
+        <v>29000</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>5</v>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>742000</v>
+      </c>
+      <c r="E52" s="3">
         <v>808000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>917000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1014000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>937000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>863000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>820000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>799000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>776000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>829000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>805000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>859000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>773000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>735000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>741000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>708000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>672000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>638000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>557000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>453000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>464000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>462000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>449000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7243000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7017000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7220000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6701000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6524000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6481000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6153000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5826000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5689000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5206000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4993000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4935000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4708000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4670000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4499000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4246000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4245000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4136000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4235000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4252000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4288000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3680000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3554000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E57" s="3">
         <v>115000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>130000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>169000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>115000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>128000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>137000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>131000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>134000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>109000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>91000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>79000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>89000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>78000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>102000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>93000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>86000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>90000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>73000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>79000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>71000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4666,80 +4797,83 @@
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>958000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1033000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1080000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1081000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1026000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>949000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>925000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>822000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>864000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>841000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>800000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>794000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>734000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>702000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>157000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>193000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>161000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>145000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>127000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>85000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>88000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>110000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>101000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
@@ -4755,80 +4889,83 @@
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>717000</v>
+      </c>
+      <c r="E59" s="3">
         <v>635000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>501000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>463000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>481000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>516000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>461000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>442000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>471000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>465000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>381000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>459000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>503000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>558000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1309000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1181000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1287000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1210000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1113000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1063000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1230000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1034000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>831000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4844,80 +4981,83 @@
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2239000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2238000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2103000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2110000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2045000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1942000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1852000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1724000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1821000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1797000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1658000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1689000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1645000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1680000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1555000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1452000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1550000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1448000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1326000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1238000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1391000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1223000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1003000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4933,80 +5073,83 @@
       <c r="AE60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4284000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4215000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4383000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3951000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3844000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3842000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3543000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3405000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3205000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2766000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2659000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2544000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2350000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2364000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>272000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>228000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>212000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>207000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>287000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>280000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>275000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>242000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>247000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,80 +5165,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E62" s="3">
         <v>292000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>178000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>157000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>91000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>114000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>112000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>108000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>121000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>128000</v>
       </c>
       <c r="N62" s="3">
         <v>128000</v>
       </c>
       <c r="O62" s="3">
+        <v>128000</v>
+      </c>
+      <c r="P62" s="3">
         <v>115000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>106000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2163000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2098000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2057000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2072000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2092000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2158000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2072000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1996000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1994000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7107000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6795000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6729000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6267000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6018000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5911000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5549000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5277000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5169000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4722000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4486000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4394000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4142000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4182000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3990000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3778000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3819000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3727000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3705000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3676000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3738000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3461000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3244000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-303000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-213000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>83000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>153000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>196000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>142000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>116000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>85000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>111000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>148000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>180000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>109000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>122000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>82000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>51000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>38000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>159000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>212000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>189000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>170000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>261000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E76" s="3">
         <v>222000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>491000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>434000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>506000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>570000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>604000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>549000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>520000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>484000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>507000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>541000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>566000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>488000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>509000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>468000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>426000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>409000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>530000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>576000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>550000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>219000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>310000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-272000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>53000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-77000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-43000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-32000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>40000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-121000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-53000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-127000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>56000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>195000</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,64 +6804,65 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E83" s="3">
         <v>20000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>8000</v>
       </c>
       <c r="N83" s="3">
         <v>8000</v>
       </c>
       <c r="O83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="P83" s="3">
         <v>15000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>10000</v>
       </c>
       <c r="V83" s="3">
         <v>10000</v>
@@ -6672,31 +6871,34 @@
         <v>10000</v>
       </c>
       <c r="X83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Y83" s="3">
         <v>8000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E89" s="3">
         <v>40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-91000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-215000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-133000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-86000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>87000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-156000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-54000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-173000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>94000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-105000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-87000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>120000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-146000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>212000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-191000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-173000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-180000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>60000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,58 +7482,59 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>59000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-95000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-29000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-14000</v>
       </c>
       <c r="J91" s="3">
         <v>-14000</v>
       </c>
       <c r="K91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-31000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-17000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-7000</v>
       </c>
       <c r="T91" s="3">
         <v>-7000</v>
@@ -7322,37 +7543,40 @@
         <v>-7000</v>
       </c>
       <c r="V91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-8000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E94" s="3">
         <v>33000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>59000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-84000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-29000</v>
       </c>
       <c r="I94" s="3">
         <v>-29000</v>
       </c>
       <c r="J94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-58000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>10000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-60000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-33000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-71000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>30000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7695,8 +7929,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7732,16 +7966,19 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E100" s="3">
         <v>28000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>137000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>263000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>94000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>61000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>106000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>86000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>54000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>42000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>91000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>42000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>73000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>43000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-71000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>67000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>18000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>292000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>14000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>83000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>30000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>35000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>30000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8140,8 +8389,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E102" s="3">
         <v>101000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>105000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-123000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-54000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>164000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-82000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-140000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>29000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>87000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-92000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-191000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>116000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-134000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>507000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>51000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-187000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>64000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
